--- a/companies/stromy/stromy-client-data-overview.xlsx
+++ b/companies/stromy/stromy-client-data-overview.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -703,7 +703,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>KEY STATISTICS</t>
+          <t>DATA SUMMARY</t>
         </is>
       </c>
     </row>
@@ -718,142 +718,89 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Founded</t>
+          <t>Total files</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>153</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Headquarters</t>
+          <t>Root JSON files</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>Logo files</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AI agent orchestration</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>DATA SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Total files</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Root JSON files</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Logo files</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
           <t>14</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Image assets</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Template files</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Font files</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Stromy  ·  Confidential — Not for distribution</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -866,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -1225,520 +1172,520 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>charter.json</t>
+          <t>business-cards/print/README.md</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>Markdown</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>15.1 KB</t>
+          <t>1.6 KB</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Brand identity spec — colors, typography, logos, images, templates</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>guidelines.md</t>
+          <t>business-cards/print/corentin-eu-print.pdf</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Markdown</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>12.5 KB</t>
+          <t>58.5 KB</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Brand usage guidelines</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>images/01_brutalist_concrete.jpg</t>
+          <t>business-cards/print/william-eu-print.pdf</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>PDF</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>4376.9 KB</t>
+          <t>58.8 KB</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>images/02_brutalist_geometric.jpg</t>
+          <t>business-cards/review/business-cards.html</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>10481.8 KB</t>
+          <t>2.9 KB</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>images/04_concrete_curves.jpg</t>
+          <t>business-cards/source/back-eu.svg</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>5038.8 KB</t>
+          <t>1.3 KB</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>images/07_geometric_bw.jpg</t>
+          <t>business-cards/source/corentin-eu-front.svg</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>1739.9 KB</t>
+          <t>1.3 KB</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>images/08_arch_lines_shadow.jpg</t>
+          <t>business-cards/source/william-eu-front.svg</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>business-cards</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>1415.8 KB</t>
+          <t>1.3 KB</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>images/11_corten_vertical_slats.jpg</t>
+          <t>charter.json</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>979.3 KB</t>
+          <t>15.0 KB</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Brand identity spec — colors, typography, logos, images, templates</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>images/12_corten_pyramid.jpg</t>
+          <t>delivery.json</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>463.0 KB</t>
+          <t>0.1 KB</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>images/13_corten_tower.jpg</t>
+          <t>fonts/Fraunces-Italic[SOFT,WONK,opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>796.0 KB</t>
+          <t>405.2 KB</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Fraunces-Italic[SOFT,WONK,opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>images/14_corten_tall_orange.jpg</t>
+          <t>fonts/Fraunces[SOFT,WONK,opsz,wght].ttf</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>182.1 KB</t>
+          <t>352.0 KB</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — Fraunces[SOFT,WONK,opsz,wght]</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>images/15_brown_concrete_lowangle.jpg</t>
+          <t>fonts/IBMPlexMono-Bold.ttf</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>204.2 KB</t>
+          <t>134.6 KB</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — IBMPlexMono-Bold</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>images/16_rusted_metal_rivets.jpg</t>
+          <t>fonts/IBMPlexMono-Regular.ttf</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>1248.1 KB</t>
+          <t>132.4 KB</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — IBMPlexMono-Regular</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>images/17_industrial_staircase.jpg</t>
+          <t>fonts/OFL-Fraunces.txt</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>1003.9 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-Fraunces</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>images/18_brown_building_monumental.jpg</t>
+          <t>fonts/OFL-IBMPlexMono.txt</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>230.7 KB</t>
+          <t>4.4 KB</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-IBMPlexMono</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>images/19_diamond_facade.jpg</t>
+          <t>fonts/OFL-PlusJakartaSans.txt</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>839.3 KB</t>
+          <t>4.3 KB</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — OFL-PlusJakartaSans</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>images/20_geometric_window_grid.jpg</t>
+          <t>fonts/PlusJakartaSans-Italic[wght].ttf</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>1787.6 KB</t>
+          <t>178.9 KB</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — PlusJakartaSans-Italic[wght]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>images/21_brutalist_bw_curves.jpg</t>
+          <t>fonts/PlusJakartaSans[wght].ttf</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>fonts</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Font TTF</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>1522.4 KB</t>
+          <t>172.2 KB</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Font file — PlusJakartaSans[wght]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>images/22_concrete_curves_sky.jpg</t>
+          <t>guidelines.md</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>Markdown</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>870.5 KB</t>
+          <t>12.5 KB</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Photography / imagery asset</t>
+          <t>Brand usage guidelines</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>images/23_vertical_fins.jpg</t>
+          <t>images/01_brutalist_concrete.jpg</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1753,7 +1700,7 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>491.2 KB</t>
+          <t>4376.9 KB</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -1765,7 +1712,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>images/24_shadow_lines_grayscale.jpg</t>
+          <t>images/02_brutalist_geometric.jpg</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -1780,7 +1727,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>356.8 KB</t>
+          <t>10481.8 KB</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -1792,7 +1739,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>images/25_tall_building_shadow.jpg</t>
+          <t>images/04_concrete_curves.jpg</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1807,7 +1754,7 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>486.8 KB</t>
+          <t>5038.8 KB</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -1819,7 +1766,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>images/26_white_concrete_daylight.jpg</t>
+          <t>images/07_geometric_bw.jpg</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -1834,7 +1781,7 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>339.7 KB</t>
+          <t>1739.9 KB</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -1846,7 +1793,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>images/27_brown_concrete_warm.jpg</t>
+          <t>images/08_arch_lines_shadow.jpg</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1861,7 +1808,7 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>988.8 KB</t>
+          <t>1415.8 KB</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
@@ -1873,7 +1820,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>images/28_metal_poles_parallel.jpg</t>
+          <t>images/11_corten_vertical_slats.jpg</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -1888,7 +1835,7 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>481.8 KB</t>
+          <t>979.3 KB</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
@@ -1900,7 +1847,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>images/29_dark_wood_floor.jpg</t>
+          <t>images/12_corten_pyramid.jpg</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1915,7 +1862,7 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>557.9 KB</t>
+          <t>463.0 KB</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -1927,7 +1874,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>images/30_weathered_barn_door.jpg</t>
+          <t>images/13_corten_tower.jpg</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -1942,7 +1889,7 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>937.9 KB</t>
+          <t>796.0 KB</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
@@ -1954,7 +1901,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>images/31_dark_wood_grain.jpg</t>
+          <t>images/14_corten_tall_orange.jpg</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1969,7 +1916,7 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>731.5 KB</t>
+          <t>182.1 KB</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -1981,7 +1928,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>images/32_amber_wood.jpg</t>
+          <t>images/15_brown_concrete_lowangle.jpg</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -1996,7 +1943,7 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>2007.7 KB</t>
+          <t>204.2 KB</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
@@ -2008,7 +1955,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>images/33_black_marble.jpg</t>
+          <t>images/16_rusted_metal_rivets.jpg</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -2023,7 +1970,7 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>633.4 KB</t>
+          <t>1248.1 KB</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -2035,7 +1982,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>images/34_dark_geometry_angular.jpg</t>
+          <t>images/17_industrial_staircase.jpg</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -2050,7 +1997,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>355.0 KB</t>
+          <t>1003.9 KB</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
@@ -2062,7 +2009,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>images/35_illuminated_windows_night.jpg</t>
+          <t>images/18_brown_building_monumental.jpg</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -2077,7 +2024,7 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>325.3 KB</t>
+          <t>230.7 KB</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr">
@@ -2089,7 +2036,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>images/36_stairwell_glass.jpg</t>
+          <t>images/19_diamond_facade.jpg</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -2104,7 +2051,7 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>1028.0 KB</t>
+          <t>839.3 KB</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
@@ -2116,7 +2063,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>images/37_glass_facade_reflections.jpg</t>
+          <t>images/20_geometric_window_grid.jpg</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -2131,7 +2078,7 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>846.4 KB</t>
+          <t>1787.6 KB</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr">
@@ -2143,7 +2090,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>images/38_dark_building_silhouette.jpg</t>
+          <t>images/21_brutalist_bw_curves.jpg</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -2158,7 +2105,7 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>956.7 KB</t>
+          <t>1522.4 KB</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
@@ -2170,7 +2117,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>images/39_industrial_pipes_bw.jpg</t>
+          <t>images/22_concrete_curves_sky.jpg</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -2185,7 +2132,7 @@
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>405.3 KB</t>
+          <t>870.5 KB</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
@@ -2197,7 +2144,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>images/40_urban_framing_post.jpg</t>
+          <t>images/23_vertical_fins.jpg</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -2212,7 +2159,7 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>654.4 KB</t>
+          <t>491.2 KB</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
@@ -2224,7 +2171,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>images/41_aerial_train_yard.jpg</t>
+          <t>images/24_shadow_lines_grayscale.jpg</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -2239,7 +2186,7 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>2543.2 KB</t>
+          <t>356.8 KB</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -2251,7 +2198,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/02_brutalist_geometric.hero-16x9.jpg</t>
+          <t>images/25_tall_building_shadow.jpg</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -2266,7 +2213,7 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>161.9 KB</t>
+          <t>486.8 KB</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
@@ -2278,7 +2225,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/02_brutalist_geometric.hero-2x1.jpg</t>
+          <t>images/26_white_concrete_daylight.jpg</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -2293,7 +2240,7 @@
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>153.9 KB</t>
+          <t>339.7 KB</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
@@ -2305,7 +2252,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/02_brutalist_geometric.hero.jpg</t>
+          <t>images/27_brown_concrete_warm.jpg</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -2320,7 +2267,7 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>169.3 KB</t>
+          <t>988.8 KB</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
@@ -2332,7 +2279,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/16_rusted_metal_rivets.hero-16x9.jpg</t>
+          <t>images/28_metal_poles_parallel.jpg</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -2347,7 +2294,7 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>307.1 KB</t>
+          <t>481.8 KB</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
@@ -2359,7 +2306,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/16_rusted_metal_rivets.hero-2x1.jpg</t>
+          <t>images/29_dark_wood_floor.jpg</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -2374,7 +2321,7 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>256.6 KB</t>
+          <t>557.9 KB</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
@@ -2386,7 +2333,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/16_rusted_metal_rivets.hero.jpg</t>
+          <t>images/30_weathered_barn_door.jpg</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -2401,7 +2348,7 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>633.9 KB</t>
+          <t>937.9 KB</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr">
@@ -2413,7 +2360,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/18_brown_building_monumental.hero-16x9.jpg</t>
+          <t>images/31_dark_wood_grain.jpg</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -2428,7 +2375,7 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>137.5 KB</t>
+          <t>731.5 KB</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
@@ -2440,7 +2387,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/18_brown_building_monumental.hero-2x1.jpg</t>
+          <t>images/32_amber_wood.jpg</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -2455,7 +2402,7 @@
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>134.9 KB</t>
+          <t>2007.7 KB</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
@@ -2467,7 +2414,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/18_brown_building_monumental.hero.jpg</t>
+          <t>images/33_black_marble.jpg</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -2482,7 +2429,7 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>137.9 KB</t>
+          <t>633.4 KB</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -2494,7 +2441,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/22_concrete_curves_sky.hero-16x9.jpg</t>
+          <t>images/34_dark_geometry_angular.jpg</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -2509,7 +2456,7 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>285.5 KB</t>
+          <t>355.0 KB</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
@@ -2521,7 +2468,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/22_concrete_curves_sky.hero-2x1.jpg</t>
+          <t>images/35_illuminated_windows_night.jpg</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -2536,7 +2483,7 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>262.8 KB</t>
+          <t>325.3 KB</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
@@ -2548,7 +2495,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/22_concrete_curves_sky.hero.jpg</t>
+          <t>images/36_stairwell_glass.jpg</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -2563,7 +2510,7 @@
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>427.3 KB</t>
+          <t>1028.0 KB</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr">
@@ -2575,7 +2522,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/25_tall_building_shadow.hero-16x9.jpg</t>
+          <t>images/37_glass_facade_reflections.jpg</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -2590,7 +2537,7 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>266.5 KB</t>
+          <t>846.4 KB</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -2602,7 +2549,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/25_tall_building_shadow.hero-2x1.jpg</t>
+          <t>images/38_dark_building_silhouette.jpg</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -2617,7 +2564,7 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>251.0 KB</t>
+          <t>956.7 KB</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -2629,7 +2576,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/25_tall_building_shadow.hero.jpg</t>
+          <t>images/39_industrial_pipes_bw.jpg</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -2644,7 +2591,7 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>278.2 KB</t>
+          <t>405.3 KB</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
@@ -2656,7 +2603,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/35_illuminated_windows_night.hero-16x9.jpg</t>
+          <t>images/40_urban_framing_post.jpg</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -2671,7 +2618,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>175.7 KB</t>
+          <t>654.4 KB</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
@@ -2683,7 +2630,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/35_illuminated_windows_night.hero-2x1.jpg</t>
+          <t>images/41_aerial_train_yard.jpg</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -2698,7 +2645,7 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>166.3 KB</t>
+          <t>2543.2 KB</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -2710,7 +2657,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/35_illuminated_windows_night.hero.jpg</t>
+          <t>images/heroes/02_brutalist_geometric.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -2725,7 +2672,7 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>185.4 KB</t>
+          <t>161.9 KB</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
@@ -2737,7 +2684,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/37_glass_facade_reflections.hero-16x9.jpg</t>
+          <t>images/heroes/02_brutalist_geometric.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -2752,7 +2699,7 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>190.9 KB</t>
+          <t>153.9 KB</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
@@ -2764,7 +2711,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/37_glass_facade_reflections.hero-2x1.jpg</t>
+          <t>images/heroes/02_brutalist_geometric.hero.jpg</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -2779,7 +2726,7 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>174.6 KB</t>
+          <t>169.3 KB</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
@@ -2791,7 +2738,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/37_glass_facade_reflections.hero.jpg</t>
+          <t>images/heroes/16_rusted_metal_rivets.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -2806,7 +2753,7 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>388.5 KB</t>
+          <t>307.1 KB</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
@@ -2818,7 +2765,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/38_dark_building_silhouette.hero-16x9.jpg</t>
+          <t>images/heroes/16_rusted_metal_rivets.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -2833,7 +2780,7 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>376.6 KB</t>
+          <t>256.6 KB</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
@@ -2845,7 +2792,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/38_dark_building_silhouette.hero-2x1.jpg</t>
+          <t>images/heroes/16_rusted_metal_rivets.hero.jpg</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -2860,7 +2807,7 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>346.3 KB</t>
+          <t>633.9 KB</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -2872,7 +2819,7 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/38_dark_building_silhouette.hero.jpg</t>
+          <t>images/heroes/18_brown_building_monumental.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -2887,7 +2834,7 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>574.5 KB</t>
+          <t>137.5 KB</t>
         </is>
       </c>
       <c r="E77" s="10" t="inlineStr">
@@ -2899,7 +2846,7 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/41_aerial_train_yard.hero-16x9.jpg</t>
+          <t>images/heroes/18_brown_building_monumental.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -2914,7 +2861,7 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>756.0 KB</t>
+          <t>134.9 KB</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -2926,7 +2873,7 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>images/heroes/41_aerial_train_yard.hero-2x1.jpg</t>
+          <t>images/heroes/18_brown_building_monumental.hero.jpg</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -2941,7 +2888,7 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>667.8 KB</t>
+          <t>137.9 KB</t>
         </is>
       </c>
       <c r="E79" s="10" t="inlineStr">
@@ -2953,7 +2900,7 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>images/heroes/41_aerial_train_yard.hero.jpg</t>
+          <t>images/heroes/22_concrete_curves_sky.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B80" s="11" t="inlineStr">
@@ -2968,7 +2915,7 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>1547.1 KB</t>
+          <t>285.5 KB</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
@@ -2980,7 +2927,7 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>images/manifest.json</t>
+          <t>images/heroes/22_concrete_curves_sky.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -2990,12 +2937,12 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>28.1 KB</t>
+          <t>262.8 KB</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -3007,7 +2954,7 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>images/processed/01_brutalist_concrete.brand.jpg</t>
+          <t>images/heroes/22_concrete_curves_sky.hero.jpg</t>
         </is>
       </c>
       <c r="B82" s="11" t="inlineStr">
@@ -3022,7 +2969,7 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>608.7 KB</t>
+          <t>427.3 KB</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
@@ -3034,7 +2981,7 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>images/processed/02_brutalist_geometric.brand.jpg</t>
+          <t>images/heroes/25_tall_building_shadow.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3049,7 +2996,7 @@
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>229.1 KB</t>
+          <t>266.5 KB</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -3061,7 +3008,7 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>images/processed/04_concrete_curves.brand.jpg</t>
+          <t>images/heroes/25_tall_building_shadow.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B84" s="11" t="inlineStr">
@@ -3076,7 +3023,7 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>1256.6 KB</t>
+          <t>251.0 KB</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
@@ -3088,7 +3035,7 @@
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>images/processed/07_geometric_bw.brand.jpg</t>
+          <t>images/heroes/25_tall_building_shadow.hero.jpg</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3103,7 +3050,7 @@
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>196.7 KB</t>
+          <t>278.2 KB</t>
         </is>
       </c>
       <c r="E85" s="10" t="inlineStr">
@@ -3115,7 +3062,7 @@
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>images/processed/08_arch_lines_shadow.brand.jpg</t>
+          <t>images/heroes/35_illuminated_windows_night.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B86" s="11" t="inlineStr">
@@ -3130,7 +3077,7 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>233.5 KB</t>
+          <t>175.7 KB</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
@@ -3142,7 +3089,7 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>images/processed/11_corten_vertical_slats.brand.jpg</t>
+          <t>images/heroes/35_illuminated_windows_night.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3157,7 +3104,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>716.2 KB</t>
+          <t>166.3 KB</t>
         </is>
       </c>
       <c r="E87" s="10" t="inlineStr">
@@ -3169,7 +3116,7 @@
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>images/processed/12_corten_pyramid.brand.jpg</t>
+          <t>images/heroes/35_illuminated_windows_night.hero.jpg</t>
         </is>
       </c>
       <c r="B88" s="11" t="inlineStr">
@@ -3184,7 +3131,7 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>288.9 KB</t>
+          <t>185.4 KB</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -3196,7 +3143,7 @@
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>images/processed/13_corten_tower.brand.jpg</t>
+          <t>images/heroes/37_glass_facade_reflections.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -3211,7 +3158,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>592.5 KB</t>
+          <t>190.9 KB</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -3223,7 +3170,7 @@
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>images/processed/14_corten_tall_orange.brand.jpg</t>
+          <t>images/heroes/37_glass_facade_reflections.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B90" s="11" t="inlineStr">
@@ -3238,7 +3185,7 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>120.9 KB</t>
+          <t>174.6 KB</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -3250,7 +3197,7 @@
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>images/processed/15_brown_concrete_lowangle.brand.jpg</t>
+          <t>images/heroes/37_glass_facade_reflections.hero.jpg</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -3265,7 +3212,7 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>140.4 KB</t>
+          <t>388.5 KB</t>
         </is>
       </c>
       <c r="E91" s="10" t="inlineStr">
@@ -3277,7 +3224,7 @@
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>images/processed/16_rusted_metal_rivets.brand.jpg</t>
+          <t>images/heroes/38_dark_building_silhouette.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B92" s="11" t="inlineStr">
@@ -3292,7 +3239,7 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>930.7 KB</t>
+          <t>376.6 KB</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -3304,7 +3251,7 @@
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>images/processed/17_industrial_staircase.brand.jpg</t>
+          <t>images/heroes/38_dark_building_silhouette.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -3319,7 +3266,7 @@
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>745.0 KB</t>
+          <t>346.3 KB</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -3331,7 +3278,7 @@
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>images/processed/18_brown_building_monumental.brand.jpg</t>
+          <t>images/heroes/38_dark_building_silhouette.hero.jpg</t>
         </is>
       </c>
       <c r="B94" s="11" t="inlineStr">
@@ -3346,7 +3293,7 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>157.5 KB</t>
+          <t>574.5 KB</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -3358,7 +3305,7 @@
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>images/processed/19_diamond_facade.brand.jpg</t>
+          <t>images/heroes/41_aerial_train_yard.hero-16x9.jpg</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -3373,7 +3320,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>607.1 KB</t>
+          <t>756.0 KB</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -3385,7 +3332,7 @@
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>images/processed/20_geometric_window_grid.brand.jpg</t>
+          <t>images/heroes/41_aerial_train_yard.hero-2x1.jpg</t>
         </is>
       </c>
       <c r="B96" s="11" t="inlineStr">
@@ -3400,7 +3347,7 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>1409.4 KB</t>
+          <t>667.8 KB</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
@@ -3412,7 +3359,7 @@
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>images/processed/21_brutalist_bw_curves.brand.jpg</t>
+          <t>images/heroes/41_aerial_train_yard.hero.jpg</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -3427,7 +3374,7 @@
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>1122.5 KB</t>
+          <t>1547.1 KB</t>
         </is>
       </c>
       <c r="E97" s="10" t="inlineStr">
@@ -3439,7 +3386,7 @@
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>images/processed/22_concrete_curves_sky.brand.jpg</t>
+          <t>images/manifest.json</t>
         </is>
       </c>
       <c r="B98" s="11" t="inlineStr">
@@ -3449,12 +3396,12 @@
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>JPEG</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>596.4 KB</t>
+          <t>28.1 KB</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
@@ -3466,7 +3413,7 @@
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>images/processed/23_vertical_fins.brand.jpg</t>
+          <t>images/processed/01_brutalist_concrete.brand.jpg</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -3481,7 +3428,7 @@
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>394.0 KB</t>
+          <t>608.7 KB</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -3493,7 +3440,7 @@
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>images/processed/24_shadow_lines_grayscale.brand.jpg</t>
+          <t>images/processed/02_brutalist_geometric.brand.jpg</t>
         </is>
       </c>
       <c r="B100" s="11" t="inlineStr">
@@ -3508,7 +3455,7 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>285.0 KB</t>
+          <t>229.1 KB</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
@@ -3520,7 +3467,7 @@
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>images/processed/25_tall_building_shadow.brand.jpg</t>
+          <t>images/processed/04_concrete_curves.brand.jpg</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -3535,7 +3482,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>392.6 KB</t>
+          <t>1256.6 KB</t>
         </is>
       </c>
       <c r="E101" s="10" t="inlineStr">
@@ -3547,7 +3494,7 @@
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>images/processed/26_white_concrete_daylight.brand.jpg</t>
+          <t>images/processed/07_geometric_bw.brand.jpg</t>
         </is>
       </c>
       <c r="B102" s="11" t="inlineStr">
@@ -3562,7 +3509,7 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>223.5 KB</t>
+          <t>196.7 KB</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -3574,7 +3521,7 @@
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>images/processed/27_brown_concrete_warm.brand.jpg</t>
+          <t>images/processed/08_arch_lines_shadow.brand.jpg</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -3589,7 +3536,7 @@
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>742.5 KB</t>
+          <t>233.5 KB</t>
         </is>
       </c>
       <c r="E103" s="10" t="inlineStr">
@@ -3601,7 +3548,7 @@
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>images/processed/28_metal_poles_parallel.brand.jpg</t>
+          <t>images/processed/11_corten_vertical_slats.brand.jpg</t>
         </is>
       </c>
       <c r="B104" s="11" t="inlineStr">
@@ -3616,7 +3563,7 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>373.0 KB</t>
+          <t>716.2 KB</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -3628,7 +3575,7 @@
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>images/processed/29_dark_wood_floor.brand.jpg</t>
+          <t>images/processed/12_corten_pyramid.brand.jpg</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -3643,7 +3590,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>398.8 KB</t>
+          <t>288.9 KB</t>
         </is>
       </c>
       <c r="E105" s="10" t="inlineStr">
@@ -3655,7 +3602,7 @@
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>images/processed/30_weathered_barn_door.brand.jpg</t>
+          <t>images/processed/13_corten_tower.brand.jpg</t>
         </is>
       </c>
       <c r="B106" s="11" t="inlineStr">
@@ -3670,7 +3617,7 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>749.6 KB</t>
+          <t>592.5 KB</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
@@ -3682,7 +3629,7 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>images/processed/31_dark_wood_grain.brand.jpg</t>
+          <t>images/processed/14_corten_tall_orange.brand.jpg</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -3697,7 +3644,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>607.1 KB</t>
+          <t>120.9 KB</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
@@ -3709,7 +3656,7 @@
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>images/processed/32_amber_wood.brand.jpg</t>
+          <t>images/processed/15_brown_concrete_lowangle.brand.jpg</t>
         </is>
       </c>
       <c r="B108" s="11" t="inlineStr">
@@ -3724,7 +3671,7 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>1625.5 KB</t>
+          <t>140.4 KB</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
@@ -3736,7 +3683,7 @@
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>images/processed/33_black_marble.brand.jpg</t>
+          <t>images/processed/16_rusted_metal_rivets.brand.jpg</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -3751,7 +3698,7 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>418.0 KB</t>
+          <t>930.7 KB</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
@@ -3763,7 +3710,7 @@
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>images/processed/34_dark_geometry_angular.brand.jpg</t>
+          <t>images/processed/17_industrial_staircase.brand.jpg</t>
         </is>
       </c>
       <c r="B110" s="11" t="inlineStr">
@@ -3778,7 +3725,7 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>209.7 KB</t>
+          <t>745.0 KB</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
@@ -3790,7 +3737,7 @@
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>images/processed/35_illuminated_windows_night.brand.jpg</t>
+          <t>images/processed/18_brown_building_monumental.brand.jpg</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -3805,7 +3752,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>256.1 KB</t>
+          <t>157.5 KB</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
@@ -3817,7 +3764,7 @@
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>images/processed/36_stairwell_glass.brand.jpg</t>
+          <t>images/processed/19_diamond_facade.brand.jpg</t>
         </is>
       </c>
       <c r="B112" s="11" t="inlineStr">
@@ -3832,7 +3779,7 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>705.2 KB</t>
+          <t>607.1 KB</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
@@ -3844,7 +3791,7 @@
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>images/processed/37_glass_facade_reflections.brand.jpg</t>
+          <t>images/processed/20_geometric_window_grid.brand.jpg</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -3859,7 +3806,7 @@
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>587.8 KB</t>
+          <t>1409.4 KB</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -3871,7 +3818,7 @@
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>images/processed/38_dark_building_silhouette.brand.jpg</t>
+          <t>images/processed/21_brutalist_bw_curves.brand.jpg</t>
         </is>
       </c>
       <c r="B114" s="11" t="inlineStr">
@@ -3886,7 +3833,7 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>688.2 KB</t>
+          <t>1122.5 KB</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
@@ -3898,7 +3845,7 @@
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>images/processed/39_industrial_pipes_bw.brand.jpg</t>
+          <t>images/processed/22_concrete_curves_sky.brand.jpg</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -3913,7 +3860,7 @@
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>288.3 KB</t>
+          <t>596.4 KB</t>
         </is>
       </c>
       <c r="E115" s="10" t="inlineStr">
@@ -3925,7 +3872,7 @@
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>images/processed/40_urban_framing_post.brand.jpg</t>
+          <t>images/processed/23_vertical_fins.brand.jpg</t>
         </is>
       </c>
       <c r="B116" s="11" t="inlineStr">
@@ -3940,7 +3887,7 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>533.6 KB</t>
+          <t>394.0 KB</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
@@ -3952,7 +3899,7 @@
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>images/processed/41_aerial_train_yard.brand.jpg</t>
+          <t>images/processed/24_shadow_lines_grayscale.brand.jpg</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -3967,7 +3914,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>2069.7 KB</t>
+          <t>285.0 KB</t>
         </is>
       </c>
       <c r="E117" s="10" t="inlineStr">
@@ -3979,654 +3926,1113 @@
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>logos/favicon.svg</t>
+          <t>images/processed/25_tall_building_shadow.brand.jpg</t>
         </is>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>0.5 KB</t>
+          <t>392.6 KB</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — favicon</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>logos/icon_dark.png</t>
+          <t>images/processed/26_white_concrete_daylight.brand.jpg</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>3.9 KB</t>
+          <t>223.5 KB</t>
         </is>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — icon_dark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>logos/icon_dark.svg</t>
+          <t>images/processed/27_brown_concrete_warm.brand.jpg</t>
         </is>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>0.5 KB</t>
+          <t>742.5 KB</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — icon_dark</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>logos/icon_green.png</t>
+          <t>images/processed/28_metal_poles_parallel.brand.jpg</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>3.9 KB</t>
+          <t>373.0 KB</t>
         </is>
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — icon_green</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>logos/icon_green.svg</t>
+          <t>images/processed/29_dark_wood_floor.brand.jpg</t>
         </is>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>0.5 KB</t>
+          <t>398.8 KB</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — icon_green</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>logos/icon_paper.png</t>
+          <t>images/processed/30_weathered_barn_door.brand.jpg</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>5.2 KB</t>
+          <t>749.6 KB</t>
         </is>
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — icon_paper</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>logos/icon_paper.svg</t>
+          <t>images/processed/31_dark_wood_grain.brand.jpg</t>
         </is>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>0.5 KB</t>
+          <t>607.1 KB</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — icon_paper</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>logos/logo.png</t>
+          <t>images/processed/32_amber_wood.brand.jpg</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>9.6 KB</t>
+          <t>1625.5 KB</t>
         </is>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>logos/logo.svg</t>
+          <t>images/processed/33_black_marble.brand.jpg</t>
         </is>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>0.8 KB</t>
+          <t>418.0 KB</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>logos/logo_mono.svg</t>
+          <t>images/processed/34_dark_geometry_angular.brand.jpg</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>0.8 KB</t>
+          <t>209.7 KB</t>
         </is>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — logo_mono</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>logos/logo_tagline.svg</t>
+          <t>images/processed/35_illuminated_windows_night.brand.jpg</t>
         </is>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>1.1 KB</t>
+          <t>256.1 KB</t>
         </is>
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo_tagline</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="129" ht="16" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>logos/logo_white.png</t>
+          <t>images/processed/36_stairwell_glass.brand.jpg</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>9.5 KB</t>
+          <t>705.2 KB</t>
         </is>
       </c>
       <c r="E129" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — logo_white</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>logos/logo_white.svg</t>
+          <t>images/processed/37_glass_facade_reflections.brand.jpg</t>
         </is>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>0.7 KB</t>
+          <t>587.8 KB</t>
         </is>
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>Logo asset — logo_white</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>logos/symbol.svg</t>
+          <t>images/processed/38_dark_building_silhouette.brand.jpg</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>logos</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>SVG</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>0.5 KB</t>
+          <t>688.2 KB</t>
         </is>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>Logo asset — symbol</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>stromy-client-data-overview.xlsx</t>
+          <t>images/processed/39_industrial_pipes_bw.brand.jpg</t>
         </is>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>XLSX</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>16.1 KB</t>
+          <t>288.3 KB</t>
         </is>
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>templates/pptx/closing.html</t>
+          <t>images/processed/40_urban_framing_post.brand.jpg</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>1.7 KB</t>
+          <t>533.6 KB</t>
         </is>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>templates/pptx/content.html</t>
+          <t>images/processed/41_aerial_train_yard.brand.jpg</t>
         </is>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>JPEG</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>2.1 KB</t>
+          <t>2069.7 KB</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Photography / imagery asset</t>
         </is>
       </c>
     </row>
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>templates/pptx/cover.html</t>
+          <t>logos/favicon.svg</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>2.4 KB</t>
+          <t>0.5 KB</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Logo asset — favicon</t>
         </is>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>templates/pptx/footer-bar.html</t>
+          <t>logos/icon_dark.png</t>
         </is>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>0.9 KB</t>
+          <t>3.9 KB</t>
         </is>
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Logo asset — icon_dark</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>templates/pptx/section-divider.html</t>
+          <t>logos/icon_dark.svg</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>templates</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>1.6 KB</t>
+          <t>0.5 KB</t>
         </is>
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>HTML template for PowerPoint slide layout</t>
+          <t>Logo asset — icon_dark</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>tokens.css</t>
+          <t>logos/icon_green.png</t>
         </is>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>root</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>15.3 KB</t>
+          <t>3.9 KB</t>
         </is>
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>CSS design tokens mapping brand colors to CSS variables</t>
+          <t>Logo asset — icon_green</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>voice/voice-anchors.md</t>
+          <t>logos/icon_green.svg</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>voice</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>Markdown</t>
+          <t>SVG</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>1.2 KB</t>
+          <t>0.5 KB</t>
         </is>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Logo asset — icon_green</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>voice/voice-extensions.json</t>
+          <t>logos/icon_paper.png</t>
         </is>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>voice</t>
+          <t>logos</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>0.4 KB</t>
+          <t>5.2 KB</t>
         </is>
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Logo asset — icon_paper</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
+          <t>logos/icon_paper.svg</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>0.5 KB</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>Logo asset — icon_paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>logos/logo.png</t>
+        </is>
+      </c>
+      <c r="B142" s="11" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>9.6 KB</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>Logo asset — logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>logos/logo.svg</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>0.8 KB</t>
+        </is>
+      </c>
+      <c r="E143" s="10" t="inlineStr">
+        <is>
+          <t>Logo asset — logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>logos/logo_mono.svg</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>0.8 KB</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>Logo asset — logo_mono</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>logos/logo_tagline.svg</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>1.1 KB</t>
+        </is>
+      </c>
+      <c r="E145" s="10" t="inlineStr">
+        <is>
+          <t>Logo asset — logo_tagline</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>logos/logo_white.png</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>PNG</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>9.5 KB</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>Logo asset — logo_white</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>logos/logo_white.svg</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>0.7 KB</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>Logo asset — logo_white</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>logos/symbol.svg</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>logos</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>SVG</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>0.5 KB</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Logo asset — symbol</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>stromy-client-data-overview.xlsx</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>XLSX</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>16.3 KB</t>
+        </is>
+      </c>
+      <c r="E149" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>templates/pptx/closing.html</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>1.7 KB</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="9" t="inlineStr">
+        <is>
+          <t>templates/pptx/content.html</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>2.1 KB</t>
+        </is>
+      </c>
+      <c r="E151" s="10" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>templates/pptx/cover.html</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>2.4 KB</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="9" t="inlineStr">
+        <is>
+          <t>templates/pptx/footer-bar.html</t>
+        </is>
+      </c>
+      <c r="B153" s="9" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>0.9 KB</t>
+        </is>
+      </c>
+      <c r="E153" s="10" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>templates/pptx/section-divider.html</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>templates</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>1.6 KB</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>HTML template for PowerPoint slide layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>tokens.css</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C155" s="9" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>15.3 KB</t>
+        </is>
+      </c>
+      <c r="E155" s="10" t="inlineStr">
+        <is>
+          <t>CSS design tokens mapping brand colors to CSS variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>voice/voice-anchors.md</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>voice</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>Markdown</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>1.2 KB</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>voice/voice-extensions.json</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="inlineStr">
+        <is>
+          <t>voice</t>
+        </is>
+      </c>
+      <c r="C157" s="9" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>0.4 KB</t>
+        </is>
+      </c>
+      <c r="E157" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
           <t>voice/voice-profile.md</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
+      <c r="B158" s="11" t="inlineStr">
         <is>
           <t>voice</t>
         </is>
       </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr">
         <is>
           <t>Markdown</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr">
+      <c r="D158" s="11" t="inlineStr">
         <is>
           <t>1.2 KB</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="8" customHeight="1"/>
-    <row r="143">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="8" customHeight="1"/>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>Stromy  ·  Confidential — Not for distribution</t>
         </is>
@@ -4635,7 +5041,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A160:F160"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
